--- a/Day-5 Logical formulas.xlsx
+++ b/Day-5 Logical formulas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\30_Days_Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8CCA0C2-2529-48F5-ACB1-90D081F04821}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F72E771C-0F21-4A31-B922-02A83535B53A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{5432E74C-7C65-42FE-96B8-92FA142AB05E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{5432E74C-7C65-42FE-96B8-92FA142AB05E}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_1" sheetId="2" r:id="rId1"/>
